--- a/ARM Functions/Battle Function Entry values.xlsx
+++ b/ARM Functions/Battle Function Entry values.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCDF7F90-1AC8-4C75-8C16-C178C0A52C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E625684-10A4-4610-8329-E319116370EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5469" yWindow="3651" windowWidth="16458" windowHeight="17915" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16466" yWindow="0" windowWidth="16466" windowHeight="17914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>When top-level timing functions are run, the registers hold specific values initially, as follows</t>
   </si>
@@ -144,22 +144,26 @@
   </si>
   <si>
     <t>offset of start of this function</t>
+  </si>
+  <si>
+    <t>Pointer to a battle state table</t>
+  </si>
+  <si>
+    <t>0815C8E0</t>
+  </si>
+  <si>
+    <t>00815C8FC</t>
+  </si>
+  <si>
+    <t>0815C868</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -171,6 +175,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -193,9 +210,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,159 +494,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="2" width="9.23046875" style="2"/>
+    <col min="3" max="3" width="18.23046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="35.07421875" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="9.23046875" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="C2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2">
+        <v>30036614</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
+      <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" s="2" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>